--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2024_25_Giornata_01.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2024_25_Giornata_01.xlsx
@@ -9896,8 +9896,8 @@
       <c r="J220" s="13">
         <v>0</v>
       </c>
-      <c r="K220" s="13">
-        <v>0</v>
+      <c r="K220" s="14">
+        <v>1</v>
       </c>
       <c r="L220" s="13">
         <v>0</v>
@@ -13753,8 +13753,8 @@
       <c r="J317" s="10">
         <v>0</v>
       </c>
-      <c r="K317" s="10">
-        <v>0</v>
+      <c r="K317" s="1">
+        <v>1</v>
       </c>
       <c r="L317" s="10">
         <v>0</v>
@@ -24705,8 +24705,8 @@
       <c r="J220" s="13">
         <v>0</v>
       </c>
-      <c r="K220" s="13">
-        <v>0</v>
+      <c r="K220" s="14">
+        <v>1</v>
       </c>
       <c r="L220" s="13">
         <v>0</v>
@@ -28562,8 +28562,8 @@
       <c r="J317" s="10">
         <v>0</v>
       </c>
-      <c r="K317" s="10">
-        <v>0</v>
+      <c r="K317" s="1">
+        <v>1</v>
       </c>
       <c r="L317" s="10">
         <v>0</v>
@@ -35251,7 +35251,7 @@
         <v>125</v>
       </c>
       <c r="D113" s="9">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E113" s="10">
         <v>0</v>
@@ -39514,8 +39514,8 @@
       <c r="J220" s="13">
         <v>0</v>
       </c>
-      <c r="K220" s="13">
-        <v>0</v>
+      <c r="K220" s="14">
+        <v>1</v>
       </c>
       <c r="L220" s="13">
         <v>0</v>
@@ -43371,8 +43371,8 @@
       <c r="J317" s="10">
         <v>0</v>
       </c>
-      <c r="K317" s="10">
-        <v>0</v>
+      <c r="K317" s="1">
+        <v>1</v>
       </c>
       <c r="L317" s="10">
         <v>0</v>
